--- a/Altium/Project Outputs for UZ_PER_SKAI3_LV_48V_410A/Rev01/BOM/BOM_UZ_PER_SKAI3_LV_48V_410A.xlsx
+++ b/Altium/Project Outputs for UZ_PER_SKAI3_LV_48V_410A/Rev01/BOM/BOM_UZ_PER_SKAI3_LV_48V_410A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UltraZohm\uz_per_skai3_lv_48v_410a\Altium\Project Outputs for UZ_PER_SKAI3_LV_48V_410A\Rev01\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01056617-A451-4836-8B09-D71809238DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{653B27B0-6B09-4241-B8EF-FBEE43456558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29184" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{A748B4CB-AB9D-4F04-B68C-3381AA6A3145}"/>
+    <workbookView xWindow="-29184" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{C9358A77-FD02-4381-A767-978D658E6F98}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_PER_SKAI3_LV_48V_410A" sheetId="1" r:id="rId1"/>
@@ -473,7 +473,7 @@
     <t>SMD resistor E24 series 12 kOhms 100mW 0603 1%</t>
   </si>
   <si>
-    <t>71-TNPW040212K3BEED</t>
+    <t>603-RT0603BRD0712K3L</t>
   </si>
   <si>
     <t>5.05k</t>
@@ -1013,7 +1013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956725DB-8AE8-4D4D-ACD2-F99CAC08BC69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9589F0B-936A-4C3D-BBB4-E134FCC5930F}">
   <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Altium/Project Outputs for UZ_PER_SKAI3_LV_48V_410A/Rev01/BOM/BOM_UZ_PER_SKAI3_LV_48V_410A.xlsx
+++ b/Altium/Project Outputs for UZ_PER_SKAI3_LV_48V_410A/Rev01/BOM/BOM_UZ_PER_SKAI3_LV_48V_410A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UltraZohm\uz_per_skai3_lv_48v_410a\Altium\Project Outputs for UZ_PER_SKAI3_LV_48V_410A\Rev01\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{653B27B0-6B09-4241-B8EF-FBEE43456558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2058BAE-5DE3-48F1-B3D6-75E2069DA138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29184" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{C9358A77-FD02-4381-A767-978D658E6F98}"/>
+    <workbookView xWindow="-29184" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{033CE1E6-1472-4D8A-B080-34C65BB13C4F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_PER_SKAI3_LV_48V_410A" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
     <t>R29, R35A, R35B, R35C, R36A, R36B, R36C, R49, R50</t>
   </si>
   <si>
-    <t>71-TNPW04025K05BEED</t>
+    <t>71-TNPW06035K05BEEA, 71-TNPW04025K05BEED</t>
   </si>
   <si>
     <t>Serial #</t>
@@ -1013,7 +1013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9589F0B-936A-4C3D-BBB4-E134FCC5930F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4A68E7-DD59-4902-AF60-9CEB96C54BEA}">
   <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Altium/Project Outputs for UZ_PER_SKAI3_LV_48V_410A/Rev01/BOM/BOM_UZ_PER_SKAI3_LV_48V_410A.xlsx
+++ b/Altium/Project Outputs for UZ_PER_SKAI3_LV_48V_410A/Rev01/BOM/BOM_UZ_PER_SKAI3_LV_48V_410A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UltraZohm\uz_per_skai3_lv_48v_410a\Altium\Project Outputs for UZ_PER_SKAI3_LV_48V_410A\Rev01\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2058BAE-5DE3-48F1-B3D6-75E2069DA138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71E87A68-2568-4D6B-A905-443C40EB7A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29184" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{033CE1E6-1472-4D8A-B080-34C65BB13C4F}"/>
+    <workbookView xWindow="-29184" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{3E882EF0-0AF4-4AE1-9520-DA9BB2E04794}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_UZ_PER_SKAI3_LV_48V_410A" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
     <t>R29, R35A, R35B, R35C, R36A, R36B, R36C, R49, R50</t>
   </si>
   <si>
-    <t>71-TNPW06035K05BEEA, 71-TNPW04025K05BEED</t>
+    <t>71-TNPW06035K05BEEA</t>
   </si>
   <si>
     <t>Serial #</t>
@@ -1013,7 +1013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4A68E7-DD59-4902-AF60-9CEB96C54BEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD13C1F-AC72-468C-8474-0EDFCC7E4B6F}">
   <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
